--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487910_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487910_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0662</v>
+        <v>4.7137</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4067</v>
+        <v>4.2872</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6596</v>
+        <v>0.4265</v>
       </c>
       <c r="G2" t="n">
         <v>2.8162</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5424</v>
+        <v>1.1899</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5129</v>
+        <v>0.3677</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0552</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.7076</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9896</v>
+        <v>1.0961</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5428</v>
+        <v>1.0645</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5532</v>
+        <v>0.0316</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2964</v>
+        <v>-0.1576</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1877</v>
+        <v>-1.1855</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1087</v>
+        <v>1.0279</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2761</v>
+        <v>0.4671</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5306</v>
+        <v>-0.6996</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7455</v>
+        <v>1.1667</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0203</v>
+        <v>-0.6247</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6571</v>
+        <v>-0.4859</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6368</v>
+        <v>-0.1388</v>
       </c>
       <c r="P3" t="n">
         <v>-0.4162</v>
@@ -688,28 +688,28 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0282</v>
+        <v>0.2725</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5153</v>
+        <v>0.4487</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5129</v>
+        <v>-0.1761</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.9188</v>
+        <v>1.3975</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.9188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>V. STEVANIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9796</v>
+        <v>0.9841</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4802</v>
+        <v>0.2623</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5006</v>
+        <v>0.7218</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2069</v>
+        <v>0.4891</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.7014</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7356</v>
+        <v>-0.2123</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2261</v>
+        <v>0.5137</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1085</v>
+        <v>0.5137</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1176</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4329</v>
+        <v>-0.0245</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5798</v>
+        <v>0.1877</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8532</v>
+        <v>-0.2123</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4351</v>
+        <v>0.4325</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1272</v>
+        <v>0.1024</v>
       </c>
       <c r="U4" t="n">
-        <v>0.308</v>
+        <v>0.3301</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1675</v>
+        <v>-0.3538</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1675</v>
+        <v>-0.3538</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4517</v>
+        <v>0.7986</v>
       </c>
       <c r="E5" t="n">
-        <v>0.743</v>
+        <v>2.3518</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2913</v>
+        <v>-1.5532</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1576</v>
+        <v>3.2964</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1855</v>
+        <v>2.1877</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0279</v>
+        <v>1.1087</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4671</v>
+        <v>3.2761</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6996</v>
+        <v>1.5306</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1667</v>
+        <v>1.7455</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6247</v>
+        <v>0.0203</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4859</v>
+        <v>0.6571</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1388</v>
+        <v>-0.6368</v>
       </c>
       <c r="P5" t="n">
         <v>-0.4162</v>
@@ -844,28 +844,28 @@
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3719</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1272</v>
+        <v>0.3244</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4991</v>
+        <v>0.5129</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3975</v>
+        <v>-2.9188</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. STEVANIC</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4022</v>
+        <v>0.6353</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2316</v>
+        <v>1.224</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6338</v>
+        <v>-0.5887</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4891</v>
+        <v>-0.2069</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7014</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2123</v>
+        <v>-0.7356</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5137</v>
+        <v>1.2261</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5137</v>
+        <v>1.1085</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0245</v>
+        <v>-1.4329</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1877</v>
+        <v>-0.5798</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2123</v>
+        <v>-0.8532</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1494</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3915</v>
+        <v>-0.129</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2421</v>
+        <v>0.2199</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4347</v>
+        <v>-0.2101</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8517</v>
+        <v>-0.7446</v>
       </c>
       <c r="F7" t="n">
-        <v>0.417</v>
+        <v>0.5345</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5254</v>
@@ -1000,13 +1000,13 @@
         <v>0.2081</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1174</v>
+        <v>0.1072</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.1957</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7441</v>
+        <v>-0.7647</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6098</v>
+        <v>-0.3955</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1343</v>
+        <v>-0.3691</v>
       </c>
       <c r="G8" t="n">
         <v>0.6455</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4835</v>
+        <v>0.4629</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2701</v>
+        <v>0.4844</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2134</v>
+        <v>-0.0215</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0743</v>
+        <v>-0.8123</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1274</v>
+        <v>-1.2765</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0532</v>
+        <v>0.4642</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6712</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1807</v>
+        <v>0.4427</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8416</v>
+        <v>0.6925</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6609</v>
+        <v>-0.2498</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. KOCIC</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3768</v>
+        <v>-1.5513</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-1.5293</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5305</v>
+        <v>-0.022</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9952</v>
+        <v>-0.3569</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5054</v>
+        <v>-1.5905</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5006</v>
+        <v>1.2336</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1195</v>
+        <v>1.8272</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8037</v>
+        <v>-1.0066</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6842</v>
+        <v>2.8338</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1147</v>
+        <v>-2.1841</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2983</v>
+        <v>-0.5839</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8164</v>
+        <v>-1.6002</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.4568</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1991</v>
+        <v>0.0543</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6336</v>
+        <v>-0.2347</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4345</v>
+        <v>0.2891</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>S. KOCIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3872</v>
+        <v>-2.1357</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1304</v>
+        <v>-1.8107</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2569</v>
+        <v>-0.325</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3569</v>
+        <v>-0.9952</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5905</v>
+        <v>0.5054</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2336</v>
+        <v>-1.5006</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8272</v>
+        <v>1.1195</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0066</v>
+        <v>1.8037</v>
       </c>
       <c r="L11" t="n">
-        <v>2.8338</v>
+        <v>-0.6842</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1841</v>
+        <v>-2.1147</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5839</v>
+        <v>-1.2983</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6002</v>
+        <v>-0.8164</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2487</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7816</v>
+        <v>0.4402</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8358</v>
+        <v>0.6692</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0542</v>
+        <v>-0.229</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.4776</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7254</v>
+        <v>-3.9545</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8114</v>
+        <v>-4.2167</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2621</v>
       </c>
       <c r="G12" t="n">
         <v>-5.2934</v>
@@ -1390,13 +1390,13 @@
         <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7137</v>
+        <v>0.4846</v>
       </c>
       <c r="T12" t="n">
-        <v>0.593</v>
+        <v>0.1877</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1207</v>
+        <v>0.2969</v>
       </c>
       <c r="V12" t="n">
         <v>0.23</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8532</v>
+        <v>-1.2008</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.435899999999999</v>
+        <v>-0.783500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4172</v>
+        <v>-0.4173</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9594</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7145999999999999</v>
+        <v>0.7145999999999995</v>
       </c>
       <c r="I13" t="n">
         <v>-2.6738</v>
       </c>
       <c r="J13" t="n">
-        <v>8.5129</v>
+        <v>8.512899999999998</v>
       </c>
       <c r="K13" t="n">
         <v>3.9207</v>
@@ -1468,16 +1468,16 @@
         <v>12.4871</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1624</v>
+        <v>4.814800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1721</v>
+        <v>2.8247</v>
       </c>
       <c r="U13" t="n">
         <v>1.9903</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1062000000000001</v>
+        <v>0.1062</v>
       </c>
       <c r="W13" t="n">
         <v>4.5285</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.861</v>
+        <v>3.3833</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0194</v>
+        <v>0.1621</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8416</v>
+        <v>3.2211</v>
       </c>
       <c r="G14" t="n">
         <v>4.4813</v>
@@ -1546,13 +1546,13 @@
         <v>2.4974</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2528</v>
+        <v>0.7751</v>
       </c>
       <c r="T14" t="n">
-        <v>1.295</v>
+        <v>0.4377</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9578</v>
+        <v>0.3374</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2633</v>
+        <v>2.5149</v>
       </c>
       <c r="E15" t="n">
-        <v>3.254</v>
+        <v>3.0397</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9906</v>
+        <v>-0.5248</v>
       </c>
       <c r="G15" t="n">
         <v>0.6881</v>
@@ -1624,13 +1624,13 @@
         <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0491</v>
+        <v>-0.7976</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0066</v>
+        <v>-0.2209</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0425</v>
+        <v>-0.5767</v>
       </c>
       <c r="V15" t="n">
         <v>1.1675</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1729</v>
+        <v>2.0761</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8197</v>
+        <v>2.8206</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3532</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4433</v>
+        <v>0.9708</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7805</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2238</v>
+        <v>1.6598</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6925</v>
+        <v>2.2773</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7763</v>
+        <v>-0.056</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4689</v>
+        <v>2.3333</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2492</v>
+        <v>-1.3065</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0041</v>
+        <v>-0.6329</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.245</v>
+        <v>-0.6735</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2727</v>
+        <v>-0.2306</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1272</v>
+        <v>-0.2705</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1455</v>
+        <v>0.0398</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.329</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.1428</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5212</v>
+        <v>1.984</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1776</v>
+        <v>1.6054</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6564</v>
+        <v>0.3786</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9708</v>
+        <v>0.4433</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7805</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6598</v>
+        <v>1.2238</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2773</v>
+        <v>1.6925</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.056</v>
+        <v>-0.7763</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3333</v>
+        <v>2.4689</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3065</v>
+        <v>-1.2492</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6329</v>
+        <v>-0.0041</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6735</v>
+        <v>-1.245</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7855</v>
+        <v>0.0838</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9134</v>
+        <v>-0.0871</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1279</v>
+        <v>0.171</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.329</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2501</v>
+        <v>1.9327</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7077</v>
+        <v>1.2435</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5424</v>
+        <v>0.6892</v>
       </c>
       <c r="G18" t="n">
         <v>1.9847</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1508</v>
+        <v>-0.4683</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4567</v>
+        <v>0.0791</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5473</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.419</v>
+        <v>-0.4089</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1837</v>
+        <v>1.3264</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7647</v>
+        <v>-1.7353</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6094000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9016</v>
+        <v>0.0737</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7763</v>
+        <v>-0.0809</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1253</v>
+        <v>0.1546</v>
       </c>
       <c r="V19" t="n">
         <v>-0.0814</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0517</v>
+        <v>-1.1192</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0351</v>
+        <v>-1.2494</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0166</v>
+        <v>0.1302</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9011</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.216</v>
+        <v>-0.2835</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2577</v>
+        <v>0.0434</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4736</v>
+        <v>-0.3268</v>
       </c>
       <c r="V20" t="n">
         <v>0.0248</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6083</v>
+        <v>-1.2766</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7471</v>
+        <v>-1.5328</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1388</v>
+        <v>0.2562</v>
       </c>
       <c r="G21" t="n">
         <v>0.2298</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6113</v>
+        <v>-0.2796</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6524</v>
+        <v>-0.4381</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0411</v>
+        <v>0.1586</v>
       </c>
       <c r="V21" t="n">
         <v>0.23</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6778</v>
+        <v>-1.8246</v>
       </c>
       <c r="E22" t="n">
         <v>-3.2072</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5294</v>
+        <v>1.3826</v>
       </c>
       <c r="G22" t="n">
         <v>0.0315</v>
@@ -2170,13 +2170,13 @@
         <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6289</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-0.7177</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0888</v>
+        <v>-0.058</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4966</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.043</v>
+        <v>-2.1397</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8982</v>
+        <v>-1.2553</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1448</v>
+        <v>-0.8844</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5121</v>
@@ -2248,13 +2248,13 @@
         <v>1.4568</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.509</v>
+        <v>-0.6058</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9786</v>
+        <v>-0.3357</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5304</v>
+        <v>-0.2701</v>
       </c>
       <c r="V23" t="n">
         <v>-0.23</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2535</v>
+        <v>-2.5542</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8571</v>
+        <v>-2.5356</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3964</v>
+        <v>-0.0186</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8475</v>
@@ -2326,13 +2326,13 @@
         <v>2.9137</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6388</v>
+        <v>-0.9396</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.721</v>
+        <v>-0.3995</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9179</v>
+        <v>-0.5401</v>
       </c>
       <c r="V24" t="n">
         <v>0.6085</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.853200000000001</v>
+        <v>2.567800000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4174000000000007</v>
+        <v>0.4174000000000011</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4359</v>
+        <v>2.1503</v>
       </c>
       <c r="G25" t="n">
         <v>1.9594</v>
@@ -2404,13 +2404,13 @@
         <v>16.6494</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.162299999999999</v>
+        <v>-3.4481</v>
       </c>
       <c r="T25" t="n">
         <v>-1.9902</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.1721</v>
+        <v>-1.4576</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1061999999999999</v>
